--- a/backend/data/financials_by_company/000690.SZ.xlsx
+++ b/backend/data/financials_by_company/000690.SZ.xlsx
@@ -687,630 +687,630 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-4922571.742236</v>
+        <v>-17114723.598852</v>
       </c>
       <c r="C2" t="n">
-        <v>0.240348</v>
+        <v>0.161822</v>
       </c>
       <c r="D2" t="n">
-        <v>1753221947.46</v>
+        <v>2157770843.49</v>
       </c>
       <c r="E2" t="n">
-        <v>-20481007.54</v>
+        <v>-105762351.56</v>
       </c>
       <c r="F2" t="n">
-        <v>-20481007.54</v>
+        <v>-105762351.56</v>
       </c>
       <c r="G2" t="n">
-        <v>705541276.5599999</v>
+        <v>824373483.76</v>
       </c>
       <c r="H2" t="n">
-        <v>644829839.1900001</v>
+        <v>776399730.45</v>
       </c>
       <c r="I2" t="n">
-        <v>6724616383.14</v>
+        <v>7880759045.66</v>
       </c>
       <c r="J2" t="n">
-        <v>1732740939.92</v>
+        <v>2052008491.93</v>
       </c>
       <c r="K2" t="n">
-        <v>1087911100.73</v>
+        <v>1275608761.48</v>
       </c>
       <c r="L2" t="n">
-        <v>-51962023.65</v>
+        <v>-208848828.62</v>
       </c>
       <c r="M2" t="n">
-        <v>159141885.57</v>
+        <v>292077896.51</v>
       </c>
       <c r="N2" t="n">
-        <v>108275199.11</v>
+        <v>85422064.84</v>
       </c>
       <c r="O2" t="n">
-        <v>721099712.357764</v>
+        <v>913021111.721148</v>
       </c>
       <c r="P2" t="n">
-        <v>705541276.5599999</v>
+        <v>824373483.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>6985191934.68</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>8355836366.17</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8921272.82</v>
+      </c>
       <c r="S2" t="n">
-        <v>933347117.39</v>
+        <v>989491058.03</v>
       </c>
       <c r="T2" t="n">
-        <v>2204816489</v>
+        <v>2169403905</v>
       </c>
       <c r="U2" t="n">
-        <v>2204816489</v>
+        <v>2169403905</v>
       </c>
       <c r="V2" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="W2" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="X2" t="n">
-        <v>705541276.5599999</v>
+        <v>824373483.76</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>705541276.5599999</v>
+        <v>824373483.76</v>
       </c>
       <c r="AA2" t="n">
-        <v>705541276.5599999</v>
+        <v>824373483.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>705541276.5599999</v>
+        <v>824373483.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>223227938.6</v>
+        <v>159157381.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>928769215.16</v>
+        <v>983530864.97</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4577902.23</v>
+        <v>-6368953.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1916427.58</v>
+        <v>-3357446.09</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>1916427.58</v>
+        <v>3357446.09</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-51962023.65</v>
+        <v>-208848828.62</v>
       </c>
       <c r="AK2" t="n">
-        <v>1095337.19</v>
+        <v>2192996.95</v>
       </c>
       <c r="AL2" t="n">
-        <v>159141885.57</v>
+        <v>292077896.51</v>
       </c>
       <c r="AM2" t="n">
-        <v>108275199.11</v>
+        <v>85422064.84</v>
       </c>
       <c r="AN2" t="n">
-        <v>918529373.91</v>
+        <v>1054812166.85</v>
       </c>
       <c r="AO2" t="n">
-        <v>260575551.54</v>
+        <v>475077320.51</v>
       </c>
       <c r="AP2" t="n">
-        <v>65568157.25</v>
+        <v>58397285.57</v>
       </c>
       <c r="AQ2" t="n">
-        <v>59522385.67</v>
+        <v>62805397.21</v>
       </c>
       <c r="AR2" t="n">
-        <v>11210364.76</v>
+        <v>17332953.73</v>
       </c>
       <c r="AS2" t="n">
-        <v>48312020.91</v>
+        <v>45472443.48</v>
       </c>
       <c r="AT2" t="n">
-        <v>72101806.2</v>
+        <v>89941636.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3887514.73</v>
+        <v>5042996.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>68214291.47</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>84898640.45999999</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8921272.82</v>
+      </c>
       <c r="AX2" t="n">
-        <v>1179104925.45</v>
+        <v>1529889487.36</v>
       </c>
       <c r="AY2" t="n">
-        <v>6724616383.14</v>
+        <v>7880759045.66</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7903721308.59</v>
+        <v>9410648533.02</v>
       </c>
       <c r="BA2" t="n">
-        <v>7903721308.59</v>
+        <v>9410648533.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-9646913.461588999</v>
+        <v>-50767577.0525</v>
       </c>
       <c r="C3" t="n">
-        <v>0.200158</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>2092380733.42</v>
+        <v>1395628883.37</v>
       </c>
       <c r="E3" t="n">
-        <v>-48196593.05</v>
+        <v>-203070308.21</v>
       </c>
       <c r="F3" t="n">
-        <v>-48196593.05</v>
+        <v>-203070308.21</v>
       </c>
       <c r="G3" t="n">
-        <v>888539014.67</v>
+        <v>183140599.31</v>
       </c>
       <c r="H3" t="n">
-        <v>702366457.27</v>
+        <v>756500314.0599999</v>
       </c>
       <c r="I3" t="n">
-        <v>8881601720.65</v>
+        <v>8904473517.440001</v>
       </c>
       <c r="J3" t="n">
-        <v>2044184140.37</v>
+        <v>1192558575.16</v>
       </c>
       <c r="K3" t="n">
-        <v>1341817683.1</v>
+        <v>436058261.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-93364887</v>
+        <v>-147347767.78</v>
       </c>
       <c r="M3" t="n">
-        <v>230925095.76</v>
+        <v>268960287.84</v>
       </c>
       <c r="N3" t="n">
-        <v>139839445.03</v>
+        <v>122278449.24</v>
       </c>
       <c r="O3" t="n">
-        <v>927088694.258411</v>
+        <v>335443330.4675</v>
       </c>
       <c r="P3" t="n">
-        <v>888539014.67</v>
+        <v>183140599.31</v>
       </c>
       <c r="Q3" t="n">
-        <v>9182154582.370001</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>9135018511.23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>215657.16</v>
+      </c>
       <c r="S3" t="n">
-        <v>1104197994.53</v>
+        <v>158225358.76</v>
       </c>
       <c r="T3" t="n">
-        <v>2167168328</v>
+        <v>2289257491</v>
       </c>
       <c r="U3" t="n">
-        <v>2167168328</v>
+        <v>2289257491</v>
       </c>
       <c r="V3" t="n">
-        <v>0.41</v>
+        <v>0.08</v>
       </c>
       <c r="W3" t="n">
-        <v>0.41</v>
+        <v>0.08</v>
       </c>
       <c r="X3" t="n">
-        <v>888539014.67</v>
+        <v>183140599.31</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>888539014.67</v>
+        <v>183140599.31</v>
       </c>
       <c r="AA3" t="n">
-        <v>888539014.67</v>
+        <v>183140599.31</v>
       </c>
       <c r="AB3" t="n">
-        <v>888539014.67</v>
+        <v>183140599.31</v>
       </c>
       <c r="AC3" t="n">
-        <v>222353572.67</v>
+        <v>-16042626.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1110892587.34</v>
+        <v>167097973.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>6694592.81</v>
+        <v>8872614.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>-83704398.37</v>
+        <v>-223232579.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>-129389.86</v>
+        <v>-190783.49</v>
       </c>
       <c r="AH3" t="n">
-        <v>3439688.23</v>
+        <v>-2908160.21</v>
       </c>
       <c r="AI3" t="n">
-        <v>80394100</v>
+        <v>226331523</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-93364887</v>
+        <v>-147347767.78</v>
       </c>
       <c r="AK3" t="n">
-        <v>2279236.27</v>
+        <v>665929.1800000001</v>
       </c>
       <c r="AL3" t="n">
-        <v>230925095.76</v>
+        <v>268960287.84</v>
       </c>
       <c r="AM3" t="n">
-        <v>139839445.03</v>
+        <v>122278449.24</v>
       </c>
       <c r="AN3" t="n">
-        <v>1092647497.68</v>
+        <v>279981685.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>300552861.72</v>
+        <v>230544993.79</v>
       </c>
       <c r="AP3" t="n">
-        <v>57095734.05</v>
+        <v>46034415.89</v>
       </c>
       <c r="AQ3" t="n">
-        <v>54227455.02</v>
+        <v>52032850.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>13822487.69</v>
+        <v>15534789.77</v>
       </c>
       <c r="AS3" t="n">
-        <v>40404967.33</v>
+        <v>36498060.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>76914939.93000001</v>
+        <v>65274574.67</v>
       </c>
       <c r="AU3" t="n">
-        <v>5117446.49</v>
+        <v>2963093.48</v>
       </c>
       <c r="AV3" t="n">
-        <v>71797493.44</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>62311481.19</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>215657.16</v>
+      </c>
       <c r="AX3" t="n">
-        <v>1393200359.4</v>
+        <v>510526679.39</v>
       </c>
       <c r="AY3" t="n">
-        <v>8881601720.65</v>
+        <v>8904473517.440001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10274802080.05</v>
+        <v>9415000196.83</v>
       </c>
       <c r="BA3" t="n">
-        <v>10274802080.05</v>
+        <v>9415000196.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-50767577.0525</v>
+        <v>-9646913.461588999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.200158</v>
       </c>
       <c r="D4" t="n">
-        <v>1395628883.37</v>
+        <v>2092380733.42</v>
       </c>
       <c r="E4" t="n">
-        <v>-203070308.21</v>
+        <v>-48196593.05</v>
       </c>
       <c r="F4" t="n">
-        <v>-203070308.21</v>
+        <v>-48196593.05</v>
       </c>
       <c r="G4" t="n">
-        <v>183140599.31</v>
+        <v>888539014.67</v>
       </c>
       <c r="H4" t="n">
-        <v>756500314.0599999</v>
+        <v>702366457.27</v>
       </c>
       <c r="I4" t="n">
-        <v>8904473517.440001</v>
+        <v>8881601720.65</v>
       </c>
       <c r="J4" t="n">
-        <v>1192558575.16</v>
+        <v>2044184140.37</v>
       </c>
       <c r="K4" t="n">
-        <v>436058261.1</v>
+        <v>1341817683.1</v>
       </c>
       <c r="L4" t="n">
-        <v>-147347767.78</v>
+        <v>-93364887</v>
       </c>
       <c r="M4" t="n">
-        <v>268960287.84</v>
+        <v>230925095.76</v>
       </c>
       <c r="N4" t="n">
-        <v>122278449.24</v>
+        <v>139839445.03</v>
       </c>
       <c r="O4" t="n">
-        <v>335443330.4675</v>
+        <v>927088694.258411</v>
       </c>
       <c r="P4" t="n">
-        <v>183140599.31</v>
+        <v>888539014.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>9135018511.23</v>
-      </c>
-      <c r="R4" t="n">
-        <v>215657.16</v>
-      </c>
+        <v>9182154582.370001</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>158225358.76</v>
+        <v>1104197994.53</v>
       </c>
       <c r="T4" t="n">
-        <v>2289257491</v>
+        <v>2167168328</v>
       </c>
       <c r="U4" t="n">
-        <v>2289257491</v>
+        <v>2167168328</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08</v>
+        <v>0.41</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08</v>
+        <v>0.41</v>
       </c>
       <c r="X4" t="n">
-        <v>183140599.31</v>
+        <v>888539014.67</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>183140599.31</v>
+        <v>888539014.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>183140599.31</v>
+        <v>888539014.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>183140599.31</v>
+        <v>888539014.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>-16042626.05</v>
+        <v>222353572.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>167097973.26</v>
+        <v>1110892587.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>8872614.5</v>
+        <v>6694592.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>-223232579.3</v>
+        <v>-83704398.37</v>
       </c>
       <c r="AG4" t="n">
-        <v>-190783.49</v>
+        <v>-129389.86</v>
       </c>
       <c r="AH4" t="n">
-        <v>-2908160.21</v>
+        <v>3439688.23</v>
       </c>
       <c r="AI4" t="n">
-        <v>226331523</v>
+        <v>80394100</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-147347767.78</v>
+        <v>-93364887</v>
       </c>
       <c r="AK4" t="n">
-        <v>665929.1800000001</v>
+        <v>2279236.27</v>
       </c>
       <c r="AL4" t="n">
-        <v>268960287.84</v>
+        <v>230925095.76</v>
       </c>
       <c r="AM4" t="n">
-        <v>122278449.24</v>
+        <v>139839445.03</v>
       </c>
       <c r="AN4" t="n">
-        <v>279981685.6</v>
+        <v>1092647497.68</v>
       </c>
       <c r="AO4" t="n">
-        <v>230544993.79</v>
+        <v>300552861.72</v>
       </c>
       <c r="AP4" t="n">
-        <v>46034415.89</v>
+        <v>57095734.05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>52032850.3</v>
+        <v>54227455.02</v>
       </c>
       <c r="AR4" t="n">
-        <v>15534789.77</v>
+        <v>13822487.69</v>
       </c>
       <c r="AS4" t="n">
-        <v>36498060.53</v>
+        <v>40404967.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>65274574.67</v>
+        <v>76914939.93000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>2963093.48</v>
+        <v>5117446.49</v>
       </c>
       <c r="AV4" t="n">
-        <v>62311481.19</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>215657.16</v>
-      </c>
+        <v>71797493.44</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>510526679.39</v>
+        <v>1393200359.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>8904473517.440001</v>
+        <v>8881601720.65</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9415000196.83</v>
+        <v>10274802080.05</v>
       </c>
       <c r="BA4" t="n">
-        <v>9415000196.83</v>
+        <v>10274802080.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-17114723.598852</v>
+        <v>-4922571.742236</v>
       </c>
       <c r="C5" t="n">
-        <v>0.161822</v>
+        <v>0.240348</v>
       </c>
       <c r="D5" t="n">
-        <v>2157770843.49</v>
+        <v>1753221947.46</v>
       </c>
       <c r="E5" t="n">
-        <v>-105762351.56</v>
+        <v>-20481007.54</v>
       </c>
       <c r="F5" t="n">
-        <v>-105762351.56</v>
+        <v>-20481007.54</v>
       </c>
       <c r="G5" t="n">
-        <v>824373483.76</v>
+        <v>705541276.5599999</v>
       </c>
       <c r="H5" t="n">
-        <v>776399730.45</v>
+        <v>644829839.1900001</v>
       </c>
       <c r="I5" t="n">
-        <v>7880759045.66</v>
+        <v>6724616383.14</v>
       </c>
       <c r="J5" t="n">
-        <v>2052008491.93</v>
+        <v>1732740939.92</v>
       </c>
       <c r="K5" t="n">
-        <v>1275608761.48</v>
+        <v>1087911100.73</v>
       </c>
       <c r="L5" t="n">
-        <v>-208848828.62</v>
+        <v>-51962023.65</v>
       </c>
       <c r="M5" t="n">
-        <v>292077896.51</v>
+        <v>159141885.57</v>
       </c>
       <c r="N5" t="n">
-        <v>85422064.84</v>
+        <v>108275199.11</v>
       </c>
       <c r="O5" t="n">
-        <v>913021111.721148</v>
+        <v>721099712.357764</v>
       </c>
       <c r="P5" t="n">
-        <v>824373483.76</v>
+        <v>705541276.5599999</v>
       </c>
       <c r="Q5" t="n">
-        <v>8355836366.17</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8921272.82</v>
-      </c>
+        <v>6985191934.68</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>989491058.03</v>
+        <v>933347117.39</v>
       </c>
       <c r="T5" t="n">
-        <v>2169403905</v>
+        <v>2204816489</v>
       </c>
       <c r="U5" t="n">
-        <v>2169403905</v>
+        <v>2204816489</v>
       </c>
       <c r="V5" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="W5" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="X5" t="n">
-        <v>824373483.76</v>
+        <v>705541276.5599999</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>824373483.76</v>
+        <v>705541276.5599999</v>
       </c>
       <c r="AA5" t="n">
-        <v>824373483.76</v>
+        <v>705541276.5599999</v>
       </c>
       <c r="AB5" t="n">
-        <v>824373483.76</v>
+        <v>705541276.5599999</v>
       </c>
       <c r="AC5" t="n">
-        <v>159157381.21</v>
+        <v>223227938.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>983530864.97</v>
+        <v>928769215.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6368953.06</v>
+        <v>-4577902.23</v>
       </c>
       <c r="AF5" t="n">
-        <v>-3357446.09</v>
+        <v>-1916427.58</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>3357446.09</v>
+        <v>1916427.58</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-208848828.62</v>
+        <v>-51962023.65</v>
       </c>
       <c r="AK5" t="n">
-        <v>2192996.95</v>
+        <v>1095337.19</v>
       </c>
       <c r="AL5" t="n">
-        <v>292077896.51</v>
+        <v>159141885.57</v>
       </c>
       <c r="AM5" t="n">
-        <v>85422064.84</v>
+        <v>108275199.11</v>
       </c>
       <c r="AN5" t="n">
-        <v>1054812166.85</v>
+        <v>918529373.91</v>
       </c>
       <c r="AO5" t="n">
-        <v>475077320.51</v>
+        <v>260575551.54</v>
       </c>
       <c r="AP5" t="n">
-        <v>58397285.57</v>
+        <v>65568157.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>62805397.21</v>
+        <v>59522385.67</v>
       </c>
       <c r="AR5" t="n">
-        <v>17332953.73</v>
+        <v>11210364.76</v>
       </c>
       <c r="AS5" t="n">
-        <v>45472443.48</v>
+        <v>48312020.91</v>
       </c>
       <c r="AT5" t="n">
-        <v>89941636.5</v>
+        <v>72101806.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>5042996.04</v>
+        <v>3887514.73</v>
       </c>
       <c r="AV5" t="n">
-        <v>84898640.45999999</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8921272.82</v>
-      </c>
+        <v>68214291.47</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>1529889487.36</v>
+        <v>1179104925.45</v>
       </c>
       <c r="AY5" t="n">
-        <v>7880759045.66</v>
+        <v>6724616383.14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9410648533.02</v>
+        <v>7903721308.59</v>
       </c>
       <c r="BA5" t="n">
-        <v>9410648533.02</v>
+        <v>7903721308.59</v>
       </c>
     </row>
   </sheetData>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>2175887862</v>
@@ -1660,40 +1660,40 @@
         <v>2175887862</v>
       </c>
       <c r="D2" t="n">
-        <v>2568602571.86</v>
+        <v>1016491244.49</v>
       </c>
       <c r="E2" t="n">
-        <v>7381452643.74</v>
+        <v>6727762602.64</v>
       </c>
       <c r="F2" t="n">
-        <v>11556822047.94</v>
+        <v>10534044034.83</v>
       </c>
       <c r="G2" t="n">
-        <v>19176495337.36</v>
+        <v>16979424090.45</v>
       </c>
       <c r="H2" t="n">
-        <v>3118088254.27</v>
+        <v>2866956647.58</v>
       </c>
       <c r="I2" t="n">
-        <v>11556822047.94</v>
+        <v>10534044034.83</v>
       </c>
       <c r="J2" t="n">
-        <v>7488940.41</v>
+        <v>41521195.79</v>
       </c>
       <c r="K2" t="n">
-        <v>12204909559.62</v>
+        <v>11183605177.59</v>
       </c>
       <c r="L2" t="n">
-        <v>18043302667.62</v>
+        <v>15696511177.59</v>
       </c>
       <c r="M2" t="n">
-        <v>12204909559.62</v>
+        <v>11183605177.59</v>
       </c>
       <c r="N2" t="n">
-        <v>12204909559.62</v>
+        <v>11183605177.59</v>
       </c>
       <c r="O2" t="n">
-        <v>5621883601.95</v>
+        <v>4843275583.52</v>
       </c>
       <c r="P2" t="n">
         <v>2942030080.08</v>
@@ -1705,144 +1705,148 @@
         <v>2175887862</v>
       </c>
       <c r="S2" t="n">
-        <v>8993846670.370001</v>
+        <v>8505453735.02</v>
       </c>
       <c r="T2" t="n">
-        <v>5851967745.87</v>
+        <v>4569302149.83</v>
       </c>
       <c r="U2" t="n">
-        <v>6085697.46</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>14847637.1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>27316.94</v>
+      </c>
       <c r="W2" t="n">
-        <v>5845882048.41</v>
+        <v>4554427195.79</v>
       </c>
       <c r="X2" t="n">
-        <v>7488940.41</v>
+        <v>41521195.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>5838393108</v>
+        <v>4512906000</v>
       </c>
       <c r="Z2" t="n">
-        <v>3141878924.5</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>3936151585.19</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8049876.1</v>
+      </c>
       <c r="AB2" t="n">
-        <v>1535570595.33</v>
+        <v>2173335406.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>1133192669.74</v>
+        <v>1282912912.86</v>
       </c>
       <c r="AD2" t="n">
-        <v>1606308329.17</v>
+        <v>1692435418.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1016428330.44</v>
+        <v>608831136.36</v>
       </c>
       <c r="AF2" t="n">
-        <v>82970227.23</v>
+        <v>205554498.34</v>
       </c>
       <c r="AG2" t="n">
-        <v>506909771.5</v>
+        <v>878049783.64</v>
       </c>
       <c r="AH2" t="n">
-        <v>21198756229.99</v>
+        <v>19689058912.61</v>
       </c>
       <c r="AI2" t="n">
-        <v>14938789051.22</v>
+        <v>12885950679.84</v>
       </c>
       <c r="AJ2" t="n">
-        <v>535841636.01</v>
+        <v>113259278.61</v>
       </c>
       <c r="AK2" t="n">
-        <v>13248294.55</v>
+        <v>24769850.12</v>
       </c>
       <c r="AL2" t="n">
-        <v>26813514.67</v>
+        <v>31043874.76</v>
       </c>
       <c r="AM2" t="n">
-        <v>673149310.98</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>632237611.95</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO2" t="n">
-        <v>673149310.98</v>
+        <v>632237611.95</v>
       </c>
       <c r="AP2" t="n">
-        <v>2283130745.18</v>
+        <v>2534205735.64</v>
       </c>
       <c r="AQ2" t="n">
-        <v>648087511.6799999</v>
+        <v>649561142.76</v>
       </c>
       <c r="AR2" t="n">
-        <v>648087511.6799999</v>
+        <v>649561142.76</v>
       </c>
       <c r="AS2" t="n">
-        <v>10755018712.63</v>
+        <v>8897819905.92</v>
       </c>
       <c r="AT2" t="n">
-        <v>-7548120851.93</v>
+        <v>-5523380492.75</v>
       </c>
       <c r="AU2" t="n">
-        <v>18303139564.56</v>
+        <v>14421200398.67</v>
       </c>
       <c r="AV2" t="n">
-        <v>4082058169.91</v>
+        <v>438803321.34</v>
       </c>
       <c r="AW2" t="n">
-        <v>1239737710.89</v>
+        <v>1098204377.06</v>
       </c>
       <c r="AX2" t="n">
-        <v>7890284905.5</v>
+        <v>7831417140.52</v>
       </c>
       <c r="AY2" t="n">
-        <v>5091058778.26</v>
+        <v>5052775559.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6259967178.77</v>
+        <v>6803108232.77</v>
       </c>
       <c r="BA2" t="n">
-        <v>578816371.7</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1797974.3</v>
-      </c>
+        <v>234386148.37</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>323338362.99</v>
+        <v>349267651.53</v>
       </c>
       <c r="BD2" t="n">
-        <v>323338362.99</v>
+        <v>349267651.53</v>
       </c>
       <c r="BE2" t="n">
-        <v>49222085.8</v>
+        <v>6250578.86</v>
       </c>
       <c r="BF2" t="n">
-        <v>848516020.4400001</v>
+        <v>1228280650.88</v>
       </c>
       <c r="BG2" t="n">
-        <v>-17225951.09</v>
+        <v>-13271347.92</v>
       </c>
       <c r="BH2" t="n">
-        <v>865741971.53</v>
+        <v>1241551998.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>4458276363.54</v>
+        <v>4984923203.13</v>
       </c>
       <c r="BJ2" t="n">
-        <v>55293157.66</v>
+        <v>205595534.76</v>
       </c>
       <c r="BK2" t="n">
-        <v>4402983205.88</v>
+        <v>4779327668.37</v>
       </c>
       <c r="BL2" t="n">
-        <v>159152306.76</v>
+        <v>172881713.96</v>
       </c>
       <c r="BM2" t="n">
-        <v>4243830899.12</v>
+        <v>4606445954.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>2175887862</v>
@@ -1851,40 +1855,40 @@
         <v>2175887862</v>
       </c>
       <c r="D3" t="n">
-        <v>1588058210.38</v>
+        <v>882963006.38</v>
       </c>
       <c r="E3" t="n">
-        <v>7316315656.21</v>
+        <v>7562792432.95</v>
       </c>
       <c r="F3" t="n">
-        <v>11463309157.67</v>
+        <v>10655252694.5</v>
       </c>
       <c r="G3" t="n">
-        <v>18443849316.87</v>
+        <v>18104956919.42</v>
       </c>
       <c r="H3" t="n">
-        <v>3787963904.04</v>
+        <v>3835367912.55</v>
       </c>
       <c r="I3" t="n">
-        <v>11463309157.67</v>
+        <v>10655252694.5</v>
       </c>
       <c r="J3" t="n">
-        <v>20212511.68</v>
+        <v>30942108.01</v>
       </c>
       <c r="K3" t="n">
-        <v>12127654393.92</v>
+        <v>11288216411.49</v>
       </c>
       <c r="L3" t="n">
-        <v>17321383427.92</v>
+        <v>16054905072.81</v>
       </c>
       <c r="M3" t="n">
-        <v>12127654393.92</v>
+        <v>11288216411.49</v>
       </c>
       <c r="N3" t="n">
-        <v>12127654393.92</v>
+        <v>11288216411.49</v>
       </c>
       <c r="O3" t="n">
-        <v>5645146273.05</v>
+        <v>4916046316.38</v>
       </c>
       <c r="P3" t="n">
         <v>2942030080.08</v>
@@ -1896,144 +1900,142 @@
         <v>2175887862</v>
       </c>
       <c r="S3" t="n">
-        <v>8679404304.540001</v>
+        <v>8808195288.48</v>
       </c>
       <c r="T3" t="n">
-        <v>5222559158.46</v>
+        <v>4809070297.43</v>
       </c>
       <c r="U3" t="n">
-        <v>8617612.779999999</v>
+        <v>11439528.1</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>5213941545.68</v>
+        <v>4797630769.33</v>
       </c>
       <c r="X3" t="n">
-        <v>20212511.68</v>
+        <v>30942108.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>5193729034</v>
+        <v>4766688661.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>3456845146.08</v>
+        <v>3999124991.05</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>2102374110.53</v>
+        <v>2765161663.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>1122465888.95</v>
+        <v>2050051846.61</v>
       </c>
       <c r="AD3" t="n">
-        <v>1354471035.55</v>
+        <v>1233963327.43</v>
       </c>
       <c r="AE3" t="n">
-        <v>547492645.9299999</v>
+        <v>560750277.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>185175291.77</v>
+        <v>62948616.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>621803097.85</v>
+        <v>610264432.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>20807058698.46</v>
+        <v>20096411699.97</v>
       </c>
       <c r="AI3" t="n">
-        <v>13562249648.34</v>
+        <v>12261918796.37</v>
       </c>
       <c r="AJ3" t="n">
-        <v>591493042.29</v>
+        <v>105870530.97</v>
       </c>
       <c r="AK3" t="n">
-        <v>17079493.69</v>
+        <v>20924671.87</v>
       </c>
       <c r="AL3" t="n">
-        <v>28145886.76</v>
+        <v>28979258.51</v>
       </c>
       <c r="AM3" t="n">
-        <v>737222805.29</v>
+        <v>702821413.47</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>737222805.29</v>
+        <v>702821413.47</v>
       </c>
       <c r="AP3" t="n">
-        <v>2472951807.08</v>
+        <v>2500366641.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>664345236.25</v>
+        <v>632963716.99</v>
       </c>
       <c r="AR3" t="n">
-        <v>664345236.25</v>
+        <v>632963716.99</v>
       </c>
       <c r="AS3" t="n">
-        <v>9047667539.889999</v>
+        <v>8266797305.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>-6926123476</v>
+        <v>-6249976491.75</v>
       </c>
       <c r="AU3" t="n">
-        <v>15973791015.89</v>
+        <v>14516773797.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1734148521.54</v>
+        <v>473995784.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>1245496624.76</v>
+        <v>1105607967.82</v>
       </c>
       <c r="AX3" t="n">
-        <v>7893378088.42</v>
+        <v>7853927862.63</v>
       </c>
       <c r="AY3" t="n">
-        <v>5100767781.17</v>
+        <v>5083242182.45</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7244809050.12</v>
+        <v>7834492903.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>735214987.04</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8032679.1</v>
-      </c>
+        <v>143543548.58</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>298411429.67</v>
+        <v>521051504.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>298411429.67</v>
+        <v>521051504.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>53661630.43</v>
+        <v>1104496.36</v>
       </c>
       <c r="BF3" t="n">
-        <v>1340551611.31</v>
+        <v>1112820473.26</v>
       </c>
       <c r="BG3" t="n">
-        <v>-15397207.11</v>
+        <v>-12041198.86</v>
       </c>
       <c r="BH3" t="n">
-        <v>1355948818.42</v>
+        <v>1124861672.12</v>
       </c>
       <c r="BI3" t="n">
-        <v>4808936712.57</v>
+        <v>6055972881.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>80800000</v>
+        <v>122195379.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>4728136712.57</v>
+        <v>5933777501.55</v>
       </c>
       <c r="BL3" t="n">
-        <v>29222595.01</v>
+        <v>34612836.4</v>
       </c>
       <c r="BM3" t="n">
-        <v>4698914117.56</v>
+        <v>5899164665.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>2175887862</v>
@@ -2042,40 +2044,40 @@
         <v>2175887862</v>
       </c>
       <c r="D4" t="n">
-        <v>882963006.38</v>
+        <v>1588058210.38</v>
       </c>
       <c r="E4" t="n">
-        <v>7562792432.95</v>
+        <v>7316315656.21</v>
       </c>
       <c r="F4" t="n">
-        <v>10655252694.5</v>
+        <v>11463309157.67</v>
       </c>
       <c r="G4" t="n">
-        <v>18104956919.42</v>
+        <v>18443849316.87</v>
       </c>
       <c r="H4" t="n">
-        <v>3835367912.55</v>
+        <v>3787963904.04</v>
       </c>
       <c r="I4" t="n">
-        <v>10655252694.5</v>
+        <v>11463309157.67</v>
       </c>
       <c r="J4" t="n">
-        <v>30942108.01</v>
+        <v>20212511.68</v>
       </c>
       <c r="K4" t="n">
-        <v>11288216411.49</v>
+        <v>12127654393.92</v>
       </c>
       <c r="L4" t="n">
-        <v>16054905072.81</v>
+        <v>17321383427.92</v>
       </c>
       <c r="M4" t="n">
-        <v>11288216411.49</v>
+        <v>12127654393.92</v>
       </c>
       <c r="N4" t="n">
-        <v>11288216411.49</v>
+        <v>12127654393.92</v>
       </c>
       <c r="O4" t="n">
-        <v>4916046316.38</v>
+        <v>5645146273.05</v>
       </c>
       <c r="P4" t="n">
         <v>2942030080.08</v>
@@ -2087,142 +2089,144 @@
         <v>2175887862</v>
       </c>
       <c r="S4" t="n">
-        <v>8808195288.48</v>
+        <v>8679404304.540001</v>
       </c>
       <c r="T4" t="n">
-        <v>4809070297.43</v>
+        <v>5222559158.46</v>
       </c>
       <c r="U4" t="n">
-        <v>11439528.1</v>
+        <v>8617612.779999999</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>4797630769.33</v>
+        <v>5213941545.68</v>
       </c>
       <c r="X4" t="n">
-        <v>30942108.01</v>
+        <v>20212511.68</v>
       </c>
       <c r="Y4" t="n">
-        <v>4766688661.32</v>
+        <v>5193729034</v>
       </c>
       <c r="Z4" t="n">
-        <v>3999124991.05</v>
+        <v>3456845146.08</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>2765161663.62</v>
+        <v>2102374110.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>2050051846.61</v>
+        <v>1122465888.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>1233963327.43</v>
+        <v>1354471035.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>560750277.76</v>
+        <v>547492645.9299999</v>
       </c>
       <c r="AF4" t="n">
-        <v>62948616.87</v>
+        <v>185175291.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>610264432.8</v>
+        <v>621803097.85</v>
       </c>
       <c r="AH4" t="n">
-        <v>20096411699.97</v>
+        <v>20807058698.46</v>
       </c>
       <c r="AI4" t="n">
-        <v>12261918796.37</v>
+        <v>13562249648.34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105870530.97</v>
+        <v>591493042.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>20924671.87</v>
+        <v>17079493.69</v>
       </c>
       <c r="AL4" t="n">
-        <v>28979258.51</v>
+        <v>28145886.76</v>
       </c>
       <c r="AM4" t="n">
-        <v>702821413.47</v>
+        <v>737222805.29</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>702821413.47</v>
+        <v>737222805.29</v>
       </c>
       <c r="AP4" t="n">
-        <v>2500366641.2</v>
+        <v>2472951807.08</v>
       </c>
       <c r="AQ4" t="n">
-        <v>632963716.99</v>
+        <v>664345236.25</v>
       </c>
       <c r="AR4" t="n">
-        <v>632963716.99</v>
+        <v>664345236.25</v>
       </c>
       <c r="AS4" t="n">
-        <v>8266797305.75</v>
+        <v>9047667539.889999</v>
       </c>
       <c r="AT4" t="n">
-        <v>-6249976491.75</v>
+        <v>-6926123476</v>
       </c>
       <c r="AU4" t="n">
-        <v>14516773797.5</v>
+        <v>15973791015.89</v>
       </c>
       <c r="AV4" t="n">
-        <v>473995784.6</v>
+        <v>1734148521.54</v>
       </c>
       <c r="AW4" t="n">
-        <v>1105607967.82</v>
+        <v>1245496624.76</v>
       </c>
       <c r="AX4" t="n">
-        <v>7853927862.63</v>
+        <v>7893378088.42</v>
       </c>
       <c r="AY4" t="n">
-        <v>5083242182.45</v>
+        <v>5100767781.17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7834492903.6</v>
+        <v>7244809050.12</v>
       </c>
       <c r="BA4" t="n">
-        <v>143543548.58</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
+        <v>735214987.04</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8032679.1</v>
+      </c>
       <c r="BC4" t="n">
-        <v>521051504.25</v>
+        <v>298411429.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>521051504.25</v>
+        <v>298411429.67</v>
       </c>
       <c r="BE4" t="n">
-        <v>1104496.36</v>
+        <v>53661630.43</v>
       </c>
       <c r="BF4" t="n">
-        <v>1112820473.26</v>
+        <v>1340551611.31</v>
       </c>
       <c r="BG4" t="n">
-        <v>-12041198.86</v>
+        <v>-15397207.11</v>
       </c>
       <c r="BH4" t="n">
-        <v>1124861672.12</v>
+        <v>1355948818.42</v>
       </c>
       <c r="BI4" t="n">
-        <v>6055972881.15</v>
+        <v>4808936712.57</v>
       </c>
       <c r="BJ4" t="n">
-        <v>122195379.6</v>
+        <v>80800000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5933777501.55</v>
+        <v>4728136712.57</v>
       </c>
       <c r="BL4" t="n">
-        <v>34612836.4</v>
+        <v>29222595.01</v>
       </c>
       <c r="BM4" t="n">
-        <v>5899164665.15</v>
+        <v>4698914117.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>2175887862</v>
@@ -2231,40 +2235,40 @@
         <v>2175887862</v>
       </c>
       <c r="D5" t="n">
-        <v>1016491244.49</v>
+        <v>2568602571.86</v>
       </c>
       <c r="E5" t="n">
-        <v>6727762602.64</v>
+        <v>7381452643.74</v>
       </c>
       <c r="F5" t="n">
-        <v>10534044034.83</v>
+        <v>11556822047.94</v>
       </c>
       <c r="G5" t="n">
-        <v>16979424090.45</v>
+        <v>19176495337.36</v>
       </c>
       <c r="H5" t="n">
-        <v>2866956647.58</v>
+        <v>3118088254.27</v>
       </c>
       <c r="I5" t="n">
-        <v>10534044034.83</v>
+        <v>11556822047.94</v>
       </c>
       <c r="J5" t="n">
-        <v>41521195.79</v>
+        <v>7488940.41</v>
       </c>
       <c r="K5" t="n">
-        <v>11183605177.59</v>
+        <v>12204909559.62</v>
       </c>
       <c r="L5" t="n">
-        <v>15696511177.59</v>
+        <v>18043302667.62</v>
       </c>
       <c r="M5" t="n">
-        <v>11183605177.59</v>
+        <v>12204909559.62</v>
       </c>
       <c r="N5" t="n">
-        <v>11183605177.59</v>
+        <v>12204909559.62</v>
       </c>
       <c r="O5" t="n">
-        <v>4843275583.52</v>
+        <v>5621883601.95</v>
       </c>
       <c r="P5" t="n">
         <v>2942030080.08</v>
@@ -2276,143 +2280,139 @@
         <v>2175887862</v>
       </c>
       <c r="S5" t="n">
-        <v>8505453735.02</v>
+        <v>8993846670.370001</v>
       </c>
       <c r="T5" t="n">
-        <v>4569302149.83</v>
+        <v>5851967745.87</v>
       </c>
       <c r="U5" t="n">
-        <v>14847637.1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>27316.94</v>
-      </c>
+        <v>6085697.46</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>4554427195.79</v>
+        <v>5845882048.41</v>
       </c>
       <c r="X5" t="n">
-        <v>41521195.79</v>
+        <v>7488940.41</v>
       </c>
       <c r="Y5" t="n">
-        <v>4512906000</v>
+        <v>5838393108</v>
       </c>
       <c r="Z5" t="n">
-        <v>3936151585.19</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>8049876.1</v>
-      </c>
+        <v>3141878924.5</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>2173335406.85</v>
+        <v>1535570595.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>1282912912.86</v>
+        <v>1133192669.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1692435418.34</v>
+        <v>1606308329.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>608831136.36</v>
+        <v>1016428330.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>205554498.34</v>
+        <v>82970227.23</v>
       </c>
       <c r="AG5" t="n">
-        <v>878049783.64</v>
+        <v>506909771.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>19689058912.61</v>
+        <v>21198756229.99</v>
       </c>
       <c r="AI5" t="n">
-        <v>12885950679.84</v>
+        <v>14938789051.22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>113259278.61</v>
+        <v>535841636.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>24769850.12</v>
+        <v>13248294.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>31043874.76</v>
+        <v>26813514.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>632237611.95</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
+        <v>673149310.98</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>632237611.95</v>
+        <v>673149310.98</v>
       </c>
       <c r="AP5" t="n">
-        <v>2534205735.64</v>
+        <v>2283130745.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>649561142.76</v>
+        <v>648087511.6799999</v>
       </c>
       <c r="AR5" t="n">
-        <v>649561142.76</v>
+        <v>648087511.6799999</v>
       </c>
       <c r="AS5" t="n">
-        <v>8897819905.92</v>
+        <v>10755018712.63</v>
       </c>
       <c r="AT5" t="n">
-        <v>-5523380492.75</v>
+        <v>-7548120851.93</v>
       </c>
       <c r="AU5" t="n">
-        <v>14421200398.67</v>
+        <v>18303139564.56</v>
       </c>
       <c r="AV5" t="n">
-        <v>438803321.34</v>
+        <v>4082058169.91</v>
       </c>
       <c r="AW5" t="n">
-        <v>1098204377.06</v>
+        <v>1239737710.89</v>
       </c>
       <c r="AX5" t="n">
-        <v>7831417140.52</v>
+        <v>7890284905.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>5052775559.75</v>
+        <v>5091058778.26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6803108232.77</v>
+        <v>6259967178.77</v>
       </c>
       <c r="BA5" t="n">
-        <v>234386148.37</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
+        <v>578816371.7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1797974.3</v>
+      </c>
       <c r="BC5" t="n">
-        <v>349267651.53</v>
+        <v>323338362.99</v>
       </c>
       <c r="BD5" t="n">
-        <v>349267651.53</v>
+        <v>323338362.99</v>
       </c>
       <c r="BE5" t="n">
-        <v>6250578.86</v>
+        <v>49222085.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1228280650.88</v>
+        <v>848516020.4400001</v>
       </c>
       <c r="BG5" t="n">
-        <v>-13271347.92</v>
+        <v>-17225951.09</v>
       </c>
       <c r="BH5" t="n">
-        <v>1241551998.8</v>
+        <v>865741971.53</v>
       </c>
       <c r="BI5" t="n">
-        <v>4984923203.13</v>
+        <v>4458276363.54</v>
       </c>
       <c r="BJ5" t="n">
-        <v>205595534.76</v>
+        <v>55293157.66</v>
       </c>
       <c r="BK5" t="n">
-        <v>4779327668.37</v>
+        <v>4402983205.88</v>
       </c>
       <c r="BL5" t="n">
-        <v>172881713.96</v>
+        <v>159152306.76</v>
       </c>
       <c r="BM5" t="n">
-        <v>4606445954.41</v>
+        <v>4243830899.12</v>
       </c>
     </row>
   </sheetData>
@@ -2658,554 +2658,554 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1109982.53</v>
+        <v>1153567144.72</v>
       </c>
       <c r="C2" t="n">
-        <v>-3824369062.19</v>
+        <v>-1292566500</v>
       </c>
       <c r="D2" t="n">
-        <v>3859942909.14</v>
+        <v>1282624048.81</v>
       </c>
       <c r="E2" t="n">
-        <v>-1678266880.66</v>
+        <v>-281221121.98</v>
       </c>
       <c r="F2" t="n">
-        <v>4277972885.54</v>
+        <v>4608007556.55</v>
       </c>
       <c r="G2" t="n">
-        <v>4700176067.75</v>
+        <v>4140508064.92</v>
       </c>
       <c r="H2" t="n">
-        <v>1484128.35</v>
+        <v>-490687.83</v>
       </c>
       <c r="I2" t="n">
-        <v>-423687310.56</v>
+        <v>467990179.46</v>
       </c>
       <c r="J2" t="n">
-        <v>-515836770.22</v>
+        <v>-972862540.98</v>
       </c>
       <c r="K2" t="n">
-        <v>325808417.05</v>
+        <v>-7849706.41</v>
       </c>
       <c r="L2" t="n">
-        <v>-877219034.22</v>
+        <v>-955070383.38</v>
       </c>
       <c r="M2" t="n">
-        <v>35573846.95</v>
+        <v>-9942451.189999999</v>
       </c>
       <c r="N2" t="n">
-        <v>35573846.95</v>
+        <v>-9942451.189999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-3824369062.19</v>
+        <v>-1292566500</v>
       </c>
       <c r="P2" t="n">
-        <v>3859942909.14</v>
+        <v>1282624048.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1587227403.53</v>
+        <v>6064453.74</v>
       </c>
       <c r="R2" t="n">
-        <v>-267868705.46</v>
+        <v>34034691.35</v>
       </c>
       <c r="S2" t="n">
-        <v>358908182.59</v>
+        <v>253250884.37</v>
       </c>
       <c r="T2" t="n">
-        <v>5587294039.22</v>
+        <v>2055319590.19</v>
       </c>
       <c r="U2" t="n">
-        <v>-5228385856.63</v>
+        <v>-1802068705.82</v>
       </c>
       <c r="V2" t="n">
-        <v>-1678266880.66</v>
+        <v>-281221121.98</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>-1678266880.66</v>
+        <v>-281221121.98</v>
       </c>
       <c r="Y2" t="n">
-        <v>1679376863.19</v>
+        <v>1434788266.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>234966825.02</v>
+        <v>-317628628.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>1265594.84</v>
+        <v>-665407.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>252062159.31</v>
+        <v>-1137822527.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>-24926933.32</v>
+        <v>-163993048.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>6566004.19</v>
+        <v>984852354.24</v>
       </c>
       <c r="AE2" t="n">
-        <v>161204519.62</v>
+        <v>295123791.96</v>
       </c>
       <c r="AF2" t="n">
-        <v>644829839.1900001</v>
+        <v>776399730.45</v>
       </c>
       <c r="AG2" t="n">
-        <v>12273000.7</v>
+        <v>18488134.11</v>
       </c>
       <c r="AH2" t="n">
-        <v>632556838.49</v>
+        <v>757911596.34</v>
       </c>
       <c r="AI2" t="n">
-        <v>-69082024.78</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>-146849156.44</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>11599.32</v>
+      </c>
       <c r="AK2" t="n">
-        <v>705541276.5599999</v>
+        <v>824373483.76</v>
       </c>
       <c r="AL2" t="n">
-        <v>1679376863.19</v>
+        <v>1434788266.7</v>
       </c>
       <c r="AM2" t="n">
-        <v>-608265963.1</v>
+        <v>-695306883.8200001</v>
       </c>
       <c r="AN2" t="n">
-        <v>-7256434082.97</v>
+        <v>-8329582672.15</v>
       </c>
       <c r="AO2" t="n">
-        <v>-268756927.18</v>
+        <v>-294732762.01</v>
       </c>
       <c r="AP2" t="n">
-        <v>-284109265.49</v>
+        <v>-586193973.99</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-6703567890.3</v>
+        <v>-7448655936.15</v>
       </c>
       <c r="AR2" t="n">
-        <v>9544076909.26</v>
+        <v>10459677822.67</v>
       </c>
       <c r="AS2" t="n">
-        <v>202757433.87</v>
+        <v>192761875.95</v>
       </c>
       <c r="AT2" t="n">
-        <v>9341319475.389999</v>
+        <v>10266915946.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>24366143.95</v>
+        <v>944771934.41</v>
       </c>
       <c r="C3" t="n">
-        <v>-3704040460.59</v>
+        <v>-2576688781.31</v>
       </c>
       <c r="D3" t="n">
-        <v>3468597868.64</v>
+        <v>3166318287.27</v>
       </c>
       <c r="E3" t="n">
-        <v>-1982596145.79</v>
+        <v>-251168378.74</v>
       </c>
       <c r="F3" t="n">
-        <v>4700176067.75</v>
+        <v>5902051507.93</v>
       </c>
       <c r="G3" t="n">
-        <v>5902051507.93</v>
+        <v>4608007556.55</v>
       </c>
       <c r="H3" t="n">
-        <v>-194573.44</v>
+        <v>-2507420.99</v>
       </c>
       <c r="I3" t="n">
-        <v>-1201680866.74</v>
+        <v>1296551372.37</v>
       </c>
       <c r="J3" t="n">
-        <v>-1208278929.39</v>
+        <v>203988428.86</v>
       </c>
       <c r="K3" t="n">
-        <v>-661960197.78</v>
+        <v>-28269035.56</v>
       </c>
       <c r="L3" t="n">
-        <v>-310876139.66</v>
+        <v>-357372041.54</v>
       </c>
       <c r="M3" t="n">
-        <v>-235442591.95</v>
+        <v>589629505.96</v>
       </c>
       <c r="N3" t="n">
-        <v>-235442591.95</v>
+        <v>589629505.96</v>
       </c>
       <c r="O3" t="n">
-        <v>-3704040460.59</v>
+        <v>-2576688781.31</v>
       </c>
       <c r="P3" t="n">
-        <v>3468597868.64</v>
+        <v>3166318287.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2000364227.09</v>
+        <v>-103377369.64</v>
       </c>
       <c r="R3" t="n">
-        <v>-110000000</v>
+        <v>44480635.32</v>
       </c>
       <c r="S3" t="n">
-        <v>92066918.7</v>
+        <v>103010373.78</v>
       </c>
       <c r="T3" t="n">
-        <v>92066918.7</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>468064961.06</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-365054587.28</v>
+      </c>
       <c r="V3" t="n">
-        <v>-1982431145.79</v>
+        <v>-250868378.74</v>
       </c>
       <c r="W3" t="n">
-        <v>165000</v>
+        <v>300000</v>
       </c>
       <c r="X3" t="n">
-        <v>-1982596145.79</v>
+        <v>-251168378.74</v>
       </c>
       <c r="Y3" t="n">
-        <v>2006962289.74</v>
+        <v>1195940313.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>285339723.17</v>
+        <v>27046581.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>833371.75</v>
+        <v>2037299.31</v>
       </c>
       <c r="AB3" t="n">
-        <v>299071433.99</v>
+        <v>152406127.42</v>
       </c>
       <c r="AC3" t="n">
-        <v>222640074.58</v>
+        <v>-171783852.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>-237205157.15</v>
+        <v>44387007.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>234770273.94</v>
+        <v>271286616.99</v>
       </c>
       <c r="AF3" t="n">
-        <v>702366457.27</v>
+        <v>756500314.0599999</v>
       </c>
       <c r="AG3" t="n">
-        <v>15044291.74</v>
+        <v>16597425.77</v>
       </c>
       <c r="AH3" t="n">
-        <v>687322165.53</v>
+        <v>739902888.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>-187757577.68</v>
+        <v>-265266377.87</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-129389.86</v>
+        <v>-190783.49</v>
       </c>
       <c r="AK3" t="n">
-        <v>888539014.67</v>
+        <v>183140599.31</v>
       </c>
       <c r="AL3" t="n">
-        <v>2006962289.74</v>
+        <v>1195940313.15</v>
       </c>
       <c r="AM3" t="n">
-        <v>-395094599.48</v>
+        <v>-127559232.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>-9244637405.620001</v>
+        <v>-9139876468.450001</v>
       </c>
       <c r="AO3" t="n">
-        <v>-214399862.46</v>
+        <v>-129252875.98</v>
       </c>
       <c r="AP3" t="n">
-        <v>-297138087.85</v>
+        <v>-282027082.66</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-8733099455.309999</v>
+        <v>-8728596509.809999</v>
       </c>
       <c r="AR3" t="n">
-        <v>11646694294.84</v>
+        <v>10463376013.82</v>
       </c>
       <c r="AS3" t="n">
-        <v>269661868.82</v>
+        <v>377331632.12</v>
       </c>
       <c r="AT3" t="n">
-        <v>11377032426.02</v>
+        <v>10086044381.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>944771934.41</v>
+        <v>24366143.95</v>
       </c>
       <c r="C4" t="n">
-        <v>-2576688781.31</v>
+        <v>-3704040460.59</v>
       </c>
       <c r="D4" t="n">
-        <v>3166318287.27</v>
+        <v>3468597868.64</v>
       </c>
       <c r="E4" t="n">
-        <v>-251168378.74</v>
+        <v>-1982596145.79</v>
       </c>
       <c r="F4" t="n">
+        <v>4700176067.75</v>
+      </c>
+      <c r="G4" t="n">
         <v>5902051507.93</v>
       </c>
-      <c r="G4" t="n">
-        <v>4608007556.55</v>
-      </c>
       <c r="H4" t="n">
-        <v>-2507420.99</v>
+        <v>-194573.44</v>
       </c>
       <c r="I4" t="n">
-        <v>1296551372.37</v>
+        <v>-1201680866.74</v>
       </c>
       <c r="J4" t="n">
-        <v>203988428.86</v>
+        <v>-1208278929.39</v>
       </c>
       <c r="K4" t="n">
-        <v>-28269035.56</v>
+        <v>-661960197.78</v>
       </c>
       <c r="L4" t="n">
-        <v>-357372041.54</v>
+        <v>-310876139.66</v>
       </c>
       <c r="M4" t="n">
-        <v>589629505.96</v>
+        <v>-235442591.95</v>
       </c>
       <c r="N4" t="n">
-        <v>589629505.96</v>
+        <v>-235442591.95</v>
       </c>
       <c r="O4" t="n">
-        <v>-2576688781.31</v>
+        <v>-3704040460.59</v>
       </c>
       <c r="P4" t="n">
-        <v>3166318287.27</v>
+        <v>3468597868.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>-103377369.64</v>
+        <v>-2000364227.09</v>
       </c>
       <c r="R4" t="n">
-        <v>44480635.32</v>
+        <v>-110000000</v>
       </c>
       <c r="S4" t="n">
-        <v>103010373.78</v>
+        <v>92066918.7</v>
       </c>
       <c r="T4" t="n">
-        <v>468064961.06</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-365054587.28</v>
-      </c>
+        <v>92066918.7</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-250868378.74</v>
+        <v>-1982431145.79</v>
       </c>
       <c r="W4" t="n">
-        <v>300000</v>
+        <v>165000</v>
       </c>
       <c r="X4" t="n">
-        <v>-251168378.74</v>
+        <v>-1982596145.79</v>
       </c>
       <c r="Y4" t="n">
-        <v>1195940313.15</v>
+        <v>2006962289.74</v>
       </c>
       <c r="Z4" t="n">
-        <v>27046581.36</v>
+        <v>285339723.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>2037299.31</v>
+        <v>833371.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>152406127.42</v>
+        <v>299071433.99</v>
       </c>
       <c r="AC4" t="n">
-        <v>-171783852.72</v>
+        <v>222640074.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>44387007.35</v>
+        <v>-237205157.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>271286616.99</v>
+        <v>234770273.94</v>
       </c>
       <c r="AF4" t="n">
-        <v>756500314.0599999</v>
+        <v>702366457.27</v>
       </c>
       <c r="AG4" t="n">
-        <v>16597425.77</v>
+        <v>15044291.74</v>
       </c>
       <c r="AH4" t="n">
-        <v>739902888.29</v>
+        <v>687322165.53</v>
       </c>
       <c r="AI4" t="n">
-        <v>-265266377.87</v>
+        <v>-187757577.68</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-190783.49</v>
+        <v>-129389.86</v>
       </c>
       <c r="AK4" t="n">
-        <v>183140599.31</v>
+        <v>888539014.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>1195940313.15</v>
+        <v>2006962289.74</v>
       </c>
       <c r="AM4" t="n">
-        <v>-127559232.22</v>
+        <v>-395094599.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>-9139876468.450001</v>
+        <v>-9244637405.620001</v>
       </c>
       <c r="AO4" t="n">
-        <v>-129252875.98</v>
+        <v>-214399862.46</v>
       </c>
       <c r="AP4" t="n">
-        <v>-282027082.66</v>
+        <v>-297138087.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-8728596509.809999</v>
+        <v>-8733099455.309999</v>
       </c>
       <c r="AR4" t="n">
-        <v>10463376013.82</v>
+        <v>11646694294.84</v>
       </c>
       <c r="AS4" t="n">
-        <v>377331632.12</v>
+        <v>269661868.82</v>
       </c>
       <c r="AT4" t="n">
-        <v>10086044381.7</v>
+        <v>11377032426.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1153567144.72</v>
+        <v>1109982.53</v>
       </c>
       <c r="C5" t="n">
-        <v>-1292566500</v>
+        <v>-3824369062.19</v>
       </c>
       <c r="D5" t="n">
-        <v>1282624048.81</v>
+        <v>3859942909.14</v>
       </c>
       <c r="E5" t="n">
-        <v>-281221121.98</v>
+        <v>-1678266880.66</v>
       </c>
       <c r="F5" t="n">
-        <v>4608007556.55</v>
+        <v>4277972885.54</v>
       </c>
       <c r="G5" t="n">
-        <v>4140508064.92</v>
+        <v>4700176067.75</v>
       </c>
       <c r="H5" t="n">
-        <v>-490687.83</v>
+        <v>1484128.35</v>
       </c>
       <c r="I5" t="n">
-        <v>467990179.46</v>
+        <v>-423687310.56</v>
       </c>
       <c r="J5" t="n">
-        <v>-972862540.98</v>
+        <v>-515836770.22</v>
       </c>
       <c r="K5" t="n">
-        <v>-7849706.41</v>
+        <v>325808417.05</v>
       </c>
       <c r="L5" t="n">
-        <v>-955070383.38</v>
+        <v>-877219034.22</v>
       </c>
       <c r="M5" t="n">
-        <v>-9942451.189999999</v>
+        <v>35573846.95</v>
       </c>
       <c r="N5" t="n">
-        <v>-9942451.189999999</v>
+        <v>35573846.95</v>
       </c>
       <c r="O5" t="n">
-        <v>-1292566500</v>
+        <v>-3824369062.19</v>
       </c>
       <c r="P5" t="n">
-        <v>1282624048.81</v>
+        <v>3859942909.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>6064453.74</v>
+        <v>-1587227403.53</v>
       </c>
       <c r="R5" t="n">
-        <v>34034691.35</v>
+        <v>-267868705.46</v>
       </c>
       <c r="S5" t="n">
-        <v>253250884.37</v>
+        <v>358908182.59</v>
       </c>
       <c r="T5" t="n">
-        <v>2055319590.19</v>
+        <v>5587294039.22</v>
       </c>
       <c r="U5" t="n">
-        <v>-1802068705.82</v>
+        <v>-5228385856.63</v>
       </c>
       <c r="V5" t="n">
-        <v>-281221121.98</v>
+        <v>-1678266880.66</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-281221121.98</v>
+        <v>-1678266880.66</v>
       </c>
       <c r="Y5" t="n">
-        <v>1434788266.7</v>
+        <v>1679376863.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>-317628628.44</v>
+        <v>234966825.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>-665407.02</v>
+        <v>1265594.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1137822527.55</v>
+        <v>252062159.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>-163993048.11</v>
+        <v>-24926933.32</v>
       </c>
       <c r="AD5" t="n">
-        <v>984852354.24</v>
+        <v>6566004.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>295123791.96</v>
+        <v>161204519.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>776399730.45</v>
+        <v>644829839.1900001</v>
       </c>
       <c r="AG5" t="n">
-        <v>18488134.11</v>
+        <v>12273000.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>757911596.34</v>
+        <v>632556838.49</v>
       </c>
       <c r="AI5" t="n">
-        <v>-146849156.44</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>11599.32</v>
-      </c>
+        <v>-69082024.78</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>824373483.76</v>
+        <v>705541276.5599999</v>
       </c>
       <c r="AL5" t="n">
-        <v>1434788266.7</v>
+        <v>1679376863.19</v>
       </c>
       <c r="AM5" t="n">
-        <v>-695306883.8200001</v>
+        <v>-608265963.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>-8329582672.15</v>
+        <v>-7256434082.97</v>
       </c>
       <c r="AO5" t="n">
-        <v>-294732762.01</v>
+        <v>-268756927.18</v>
       </c>
       <c r="AP5" t="n">
-        <v>-586193973.99</v>
+        <v>-284109265.49</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-7448655936.15</v>
+        <v>-6703567890.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>10459677822.67</v>
+        <v>9544076909.26</v>
       </c>
       <c r="AS5" t="n">
-        <v>192761875.95</v>
+        <v>202757433.87</v>
       </c>
       <c r="AT5" t="n">
-        <v>10266915946.72</v>
+        <v>9341319475.389999</v>
       </c>
     </row>
   </sheetData>
@@ -3790,187 +3790,187 @@
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EU1" t="inlineStr">
@@ -4065,34 +4065,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>5.82</v>
+        <v>5.14</v>
       </c>
       <c r="T2" t="n">
-        <v>5.24</v>
+        <v>5.4</v>
       </c>
       <c r="U2" t="n">
-        <v>5.76</v>
+        <v>4.97</v>
       </c>
       <c r="V2" t="n">
-        <v>6.4</v>
+        <v>5.14</v>
       </c>
       <c r="W2" t="n">
-        <v>5.82</v>
+        <v>5.14</v>
       </c>
       <c r="X2" t="n">
-        <v>5.24</v>
+        <v>5.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.76</v>
+        <v>4.97</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.4</v>
+        <v>5.14</v>
       </c>
       <c r="AA2" t="n">
         <v>0.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.46</v>
+        <v>7.81</v>
       </c>
       <c r="AC2" t="n">
         <v>1779408000</v>
@@ -4104,40 +4104,40 @@
         <v>2.35</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.409</v>
+        <v>0.481</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.170213</v>
+        <v>10.893617</v>
       </c>
       <c r="AH2" t="n">
-        <v>11.462962</v>
+        <v>9.481481</v>
       </c>
       <c r="AI2" t="n">
-        <v>383955848</v>
+        <v>85927673</v>
       </c>
       <c r="AJ2" t="n">
-        <v>383955848</v>
+        <v>85927673</v>
       </c>
       <c r="AK2" t="n">
-        <v>149701739</v>
+        <v>155728990</v>
       </c>
       <c r="AL2" t="n">
-        <v>160367278</v>
+        <v>114247257</v>
       </c>
       <c r="AM2" t="n">
-        <v>160367278</v>
+        <v>114247257</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.18</v>
+        <v>5.11</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.19</v>
+        <v>5.12</v>
       </c>
       <c r="AP2" t="n">
-        <v>13468745728</v>
+        <v>11140545536</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13468745865</v>
+        <v>11184063610</v>
       </c>
       <c r="AR2" t="n">
         <v>4.18</v>
@@ -4152,19 +4152,19 @@
         <v>0.474687</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.5389448</v>
+        <v>1.2729236</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2512</v>
+        <v>5.3756</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.7324</v>
+        <v>4.78295</v>
       </c>
       <c r="AY2" t="n">
         <v>0.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.042955324</v>
+        <v>0.048638135</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -4175,13 +4175,13 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>15634774016</v>
+        <v>13306574848</v>
       </c>
       <c r="BD2" t="n">
         <v>0.11823</v>
       </c>
       <c r="BE2" t="n">
-        <v>1771869004</v>
+        <v>1769975981</v>
       </c>
       <c r="BF2" t="n">
         <v>2175887862</v>
@@ -4190,7 +4190,7 @@
         <v>0.23319</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.07786</v>
+        <v>0.07787000400000001</v>
       </c>
       <c r="BI2" t="n">
         <v>2175887862</v>
@@ -4199,7 +4199,7 @@
         <v>6.016</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.0289229</v>
+        <v>0.85106385</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4231,16 +4231,16 @@
         <v>1268956800</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.786</v>
+        <v>1.52</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.217000000000001</v>
+        <v>6.994</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.4428904</v>
+        <v>0.1898148</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
         <v>0.2</v>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>6.19</v>
+        <v>5.12</v>
       </c>
       <c r="CC2" t="n">
         <v>8.539999999999999</v>
@@ -4371,33 +4371,37 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>854415000000</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.3699999</v>
+      <c r="DJ2" t="n">
+        <v>-0.01999998</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>4.97 - 5.14</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>5.76 - 6.4</t>
+          <t>GUANGDONG BAOLIHUA NEW ENERGY S</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Guangdong Baolihua New Energy Stock Co., Ltd.</t>
         </is>
       </c>
       <c r="DO2" t="n">
-        <v>149701739</v>
+        <v>155728990</v>
       </c>
       <c r="DP2" t="n">
-        <v>2.0100002</v>
+        <v>0.94000006</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.4808613</v>
+        <v>0.22488041</v>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
@@ -4405,13 +4409,13 @@
         </is>
       </c>
       <c r="DS2" t="n">
-        <v>-0.21000004</v>
+        <v>-1.2800002</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0.032812506</v>
+        <v>-0.20000003</v>
       </c>
       <c r="DU2" t="n">
-        <v>44.28904</v>
+        <v>18.98148</v>
       </c>
       <c r="DV2" t="n">
         <v>1666349940</v>
@@ -4420,91 +4424,87 @@
         <v>1666612800</v>
       </c>
       <c r="DX2" t="n">
-        <v>6.357386</v>
+        <v>0.47</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.19</v>
+        <v>0.54</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.47</v>
+        <v>-0.25559998</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.54</v>
+        <v>-0.04754818</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.93879986</v>
+        <v>0.33704996</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.17877816</v>
+        <v>0.07046905000000001</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.4576001</v>
+        <v>15</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.3080044</v>
-      </c>
-      <c r="EF2" t="n">
         <v>15</v>
       </c>
-      <c r="EG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EH2" t="b">
+      <c r="EF2" t="b">
         <v>0</v>
       </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>GUANGDONG BAOLIHUA NEW ENERGY S</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>Guangdong Baolihua New Energy Stock Co., Ltd.</t>
-        </is>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>1782111885</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.38910472</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>5.12</v>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>PREPRE</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>1780038288</v>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>finmb_9734979</t>
+        </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>SHZ</t>
+          <t>Asia/Shanghai</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>finmb_9734979</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="EP2" t="n">
+        <v>28800000</v>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="ER2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="ET2" t="b">
+      <c r="ER2" t="b">
         <v>0</v>
+      </c>
+      <c r="ES2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>854415000000</v>
       </c>
       <c r="EU2" t="inlineStr"/>
     </row>
